--- a/healthcare_forms/030_emergency_care_plan_form--healthcare_forms.xlsx
+++ b/healthcare_forms/030_emergency_care_plan_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,8 +619,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'primary-contact',_'label':_'primary_contact',_'type':_'text',_'options':_[]}</t>
+          <t>primary_contact</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'primary-contact', 'label': 'Primary Contact', 'type': 'text', 'options': []}</t>
+          <t>Primary Contact</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'secondary-contact',_'label':_'secondary_contact',_'type':_'text',_'options':_[]}</t>
+          <t>secondary_contact</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'secondary-contact', 'label': 'Secondary Contact', 'type': 'text', 'options': []}</t>
+          <t>Secondary Contact</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'doctor-name',_'label':_"doctor's_name",_'type':_'text',_'options':_[]}</t>
+          <t>doctor's_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'doctor-name', 'label': "Doctor's Name", 'type': 'text', 'options': []}</t>
+          <t>Doctor's Name</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'doctor-phone',_'label':_"doctor's_phone",_'type':_'phone',_'options':_[]}</t>
+          <t>doctor's_phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'doctor-phone', 'label': "Doctor's Phone", 'type': 'phone', 'options': []}</t>
+          <t>Doctor's Phone</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'medications-1',_'label':_'none',_'type':_'text',_'options':_[]}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'medications-1', 'label': 'None', 'type': 'text', 'options': []}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'medications-2',_'label':_'aspirin',_'type':_'text',_'options':_[]}</t>
+          <t>aspirin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'medications-2', 'label': 'Aspirin', 'type': 'text', 'options': []}</t>
+          <t>Aspirin</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'medications-3',_'label':_'blood_pressure_medication',_'type':_'text',_'options':_[]}</t>
+          <t>blood_pressure_medication</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'medications-3', 'label': 'Blood Pressure Medication', 'type': 'text', 'options': []}</t>
+          <t>Blood Pressure Medication</t>
         </is>
       </c>
     </row>
@@ -767,12 +767,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'medications-4',_'label':_'insuline',_'type':_'text',_'options':_[]}</t>
+          <t>insuline</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'medications-4', 'label': 'Insuline', 'type': 'text', 'options': []}</t>
+          <t>Insuline</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'medications-5',_'label':_'oxygen',_'type':_'text',_'options':_[]}</t>
+          <t>oxygen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'medications-5', 'label': 'Oxygen', 'type': 'text', 'options': []}</t>
+          <t>Oxygen</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_26,_'name':_'medications-6',_'label':_'other',_'type':_'text',_'options':_[]}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 26, 'name': 'medications-6', 'label': 'Other', 'type': 'text', 'options': []}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
